--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.618193703988482</v>
+        <v>0.4254564768981284</v>
       </c>
       <c r="D2" t="n">
-        <v>1.948782929616748</v>
+        <v>0.3166772260627216</v>
       </c>
       <c r="E2" t="n">
-        <v>13.7796836877983</v>
+        <v>2.239198599267223</v>
       </c>
       <c r="F2" t="n">
-        <v>10.79470933089908</v>
+        <v>1.754140266271101</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.92933777501041</v>
+        <v>3.076017388439191</v>
       </c>
       <c r="D3" t="n">
-        <v>20.24412522171386</v>
+        <v>3.289670348528502</v>
       </c>
       <c r="E3" t="n">
-        <v>13.7796836877983</v>
+        <v>2.239198599267223</v>
       </c>
       <c r="F3" t="n">
-        <v>10.79470933089908</v>
+        <v>1.754140266271101</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.90465124529301</v>
+        <v>3.722005827360115</v>
       </c>
       <c r="D4" t="n">
-        <v>35.52119226242849</v>
+        <v>5.772193742644629</v>
       </c>
       <c r="E4" t="n">
-        <v>13.7796836877983</v>
+        <v>2.239198599267223</v>
       </c>
       <c r="F4" t="n">
-        <v>10.79470933089908</v>
+        <v>1.754140266271101</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.52941637606646</v>
+        <v>6.423530161110801</v>
       </c>
       <c r="D5" t="n">
-        <v>24.07636041883098</v>
+        <v>3.912408568060034</v>
       </c>
       <c r="E5" t="n">
-        <v>13.7796836877983</v>
+        <v>2.239198599267223</v>
       </c>
       <c r="F5" t="n">
-        <v>10.79470933089908</v>
+        <v>1.754140266271101</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.958871389296171</v>
+        <v>0.4808166007606278</v>
       </c>
       <c r="D6" t="n">
-        <v>20.44182364056005</v>
+        <v>3.321796341591008</v>
       </c>
       <c r="E6" t="n">
-        <v>13.7796836877983</v>
+        <v>2.239198599267223</v>
       </c>
       <c r="F6" t="n">
-        <v>10.79470933089908</v>
+        <v>1.754140266271101</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
